--- a/docs/exports/P38-TurboCharger-v2.xlsx
+++ b/docs/exports/P38-TurboCharger-v2.xlsx
@@ -42,7 +42,7 @@
     <t>Gerado em</t>
   </si>
   <si>
-    <t>2026-10-07T13:19:02.935Z</t>
+    <t>2026-10-07T16:50:43.293Z</t>
   </si>
   <si>
     <t>Cód. interno</t>
